--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/04_Kunden_Lizenzen/04_Kundenvertragsmatrix.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/04_Kunden_Lizenzen/04_Kundenvertragsmatrix.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top_Kunden" sheetId="1" r:id="Read0a38d21a04c08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vertragsunterlagen" sheetId="2" r:id="R94fdb5638cba41e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Umsatzabgleich" sheetId="3" r:id="R1ff53e708e6a4571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top_Kunden" sheetId="1" r:id="Rad9fbd4c94634ebf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vertragsunterlagen" sheetId="2" r:id="Rf60710bffc194799"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Umsatzabgleich" sheetId="3" r:id="Rbce7ca4bdfe143c6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/04_Kunden_Lizenzen/04_Kundenvertragsmatrix.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/04_Kunden_Lizenzen/04_Kundenvertragsmatrix.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top_Kunden" sheetId="1" r:id="Rad9fbd4c94634ebf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vertragsunterlagen" sheetId="2" r:id="Rf60710bffc194799"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Umsatzabgleich" sheetId="3" r:id="Rbce7ca4bdfe143c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top_Kunden" sheetId="1" r:id="R2427e1697ee74a94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vertragsunterlagen" sheetId="2" r:id="R2b7d11fa049c4dde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Umsatzabgleich" sheetId="3" r:id="Re4b6aa8992414f5e"/>
   </x:sheets>
 </x:workbook>
 </file>
